--- a/DOSSIES_MULTIFORMATO/SEAD/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEAD/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2027-09-30</t>
         </is>
       </c>
     </row>
